--- a/shadow_report_weekly.xlsx
+++ b/shadow_report_weekly.xlsx
@@ -589,7 +589,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This week: 2026-W41  |  Last week: 2026-W40  |  Generated: 2026-10-10 IST</t>
+          <t>This week: 2026-W42  |  Last week: 2026-W41  |  Generated: 2026-10-17 IST</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-W38 n / WR</t>
+          <t>2026-W39 n / WR</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026-W39 n / WR</t>
+          <t>2026-W40 n / WR</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-W40 n / WR</t>
+          <t>2026-W41 n / WR</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-W41 n / WR</t>
+          <t>2026-W42 n / WR</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>n=10  WR=0%</t>
+          <t>n=6  WR=0%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>n=6  WR=0%</t>
+          <t>n=0  WR=0%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/shadow_report_weekly.xlsx
+++ b/shadow_report_weekly.xlsx
@@ -589,7 +589,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This week: 2026-W42  |  Last week: 2026-W41  |  Generated: 2026-10-17 IST</t>
+          <t>This week: 2026-W43  |  Last week: 2026-W42  |  Generated: 2026-10-24 IST</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-W39 n / WR</t>
+          <t>2026-W40 n / WR</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026-W40 n / WR</t>
+          <t>2026-W41 n / WR</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-W41 n / WR</t>
+          <t>2026-W42 n / WR</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-W42 n / WR</t>
+          <t>2026-W43 n / WR</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>n=6  WR=0%</t>
+          <t>n=0  WR=0%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">

--- a/shadow_report_weekly.xlsx
+++ b/shadow_report_weekly.xlsx
@@ -589,7 +589,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This week: 2026-W43  |  Last week: 2026-W42  |  Generated: 2026-10-24 IST</t>
+          <t>This week: 2026-W44  |  Last week: 2026-W43  |  Generated: 2026-10-31 IST</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-W40 n / WR</t>
+          <t>2026-W41 n / WR</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026-W41 n / WR</t>
+          <t>2026-W42 n / WR</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-W42 n / WR</t>
+          <t>2026-W43 n / WR</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-W43 n / WR</t>
+          <t>2026-W44 n / WR</t>
         </is>
       </c>
     </row>
